--- a/static/oldsite/202/SAR_2022.xlsx
+++ b/static/oldsite/202/SAR_2022.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B2EDA0-0492-4529-9F2D-80081D4F0A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sedi-territoriali" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="86">
   <si>
     <t>nome</t>
   </si>
@@ -260,9 +266,6 @@
   </si>
   <si>
     <t>Palau</t>
-  </si>
-  <si>
-    <t>Marmillata</t>
   </si>
   <si>
     <t>ITI G. M. Angioy</t>
@@ -280,7 +283,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -494,9 +497,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -534,9 +537,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -571,7 +574,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -606,7 +609,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -779,24 +782,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L80"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" style="19" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="19" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -831,7 +834,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>14</v>
       </c>
@@ -867,7 +870,7 @@
       </c>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>26</v>
       </c>
@@ -903,7 +906,7 @@
       </c>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
@@ -939,7 +942,7 @@
       </c>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>25</v>
       </c>
@@ -975,7 +978,7 @@
       </c>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>29</v>
       </c>
@@ -1011,7 +1014,7 @@
       </c>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>27</v>
       </c>
@@ -1047,7 +1050,7 @@
       </c>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>26</v>
       </c>
@@ -1083,7 +1086,7 @@
       </c>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>26</v>
       </c>
@@ -1119,7 +1122,7 @@
       </c>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
@@ -1155,7 +1158,7 @@
       </c>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>21</v>
       </c>
@@ -1191,7 +1194,7 @@
       </c>
       <c r="L11" s="6"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
@@ -1227,7 +1230,7 @@
       </c>
       <c r="L12" s="6"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>18</v>
       </c>
@@ -1263,7 +1266,7 @@
       </c>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>24</v>
       </c>
@@ -1299,7 +1302,7 @@
       </c>
       <c r="L14" s="6"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>15</v>
       </c>
@@ -1335,7 +1338,7 @@
       </c>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
@@ -1371,7 +1374,7 @@
       </c>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>19</v>
       </c>
@@ -1407,7 +1410,7 @@
       </c>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>17</v>
       </c>
@@ -1443,7 +1446,7 @@
       </c>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>14</v>
       </c>
@@ -1479,7 +1482,7 @@
       </c>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>16</v>
       </c>
@@ -1515,7 +1518,7 @@
       </c>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
@@ -1551,7 +1554,7 @@
       </c>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>12</v>
       </c>
@@ -1587,7 +1590,7 @@
       </c>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>6</v>
       </c>
@@ -1623,7 +1626,7 @@
       </c>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>5</v>
       </c>
@@ -1659,7 +1662,7 @@
       </c>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>16</v>
       </c>
@@ -1695,7 +1698,7 @@
       </c>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>17</v>
       </c>
@@ -1731,7 +1734,7 @@
       </c>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>78</v>
       </c>
@@ -1767,16 +1770,10 @@
       </c>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="5">
-        <v>37990</v>
-      </c>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="7"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="5"/>
       <c r="D28" s="4">
         <v>4</v>
       </c>
@@ -1787,14 +1784,14 @@
         <v>1</v>
       </c>
       <c r="G28" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="I28" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="J28" s="4" t="s">
         <v>35</v>
       </c>
@@ -1803,12 +1800,12 @@
       </c>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C29" s="11">
         <v>38715</v>
@@ -1823,14 +1820,14 @@
         <v>2</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="I29" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I29" s="10" t="s">
-        <v>85</v>
-      </c>
       <c r="J29" s="10" t="s">
         <v>35</v>
       </c>
@@ -1839,7 +1836,7 @@
       </c>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
@@ -1853,7 +1850,7 @@
       <c r="K30" s="4"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
@@ -1867,7 +1864,7 @@
       <c r="K31" s="4"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
@@ -1881,7 +1878,7 @@
       <c r="K32" s="4"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
@@ -1895,7 +1892,7 @@
       <c r="K33" s="4"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
@@ -1909,7 +1906,7 @@
       <c r="K34" s="4"/>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
@@ -1923,7 +1920,7 @@
       <c r="K35" s="4"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
@@ -1937,7 +1934,7 @@
       <c r="K36" s="4"/>
       <c r="L36" s="6"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
@@ -1951,7 +1948,7 @@
       <c r="K37" s="4"/>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
@@ -1965,7 +1962,7 @@
       <c r="K38" s="4"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
@@ -1979,7 +1976,7 @@
       <c r="K39" s="4"/>
       <c r="L39" s="6"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
@@ -1993,7 +1990,7 @@
       <c r="K40" s="4"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
@@ -2007,7 +2004,7 @@
       <c r="K41" s="4"/>
       <c r="L41" s="6"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
@@ -2021,7 +2018,7 @@
       <c r="K42" s="4"/>
       <c r="L42" s="6"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
@@ -2035,7 +2032,7 @@
       <c r="K43" s="4"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
@@ -2049,7 +2046,7 @@
       <c r="K44" s="4"/>
       <c r="L44" s="6"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
@@ -2063,7 +2060,7 @@
       <c r="K45" s="4"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
@@ -2077,7 +2074,7 @@
       <c r="K46" s="4"/>
       <c r="L46" s="6"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
@@ -2091,7 +2088,7 @@
       <c r="K47" s="4"/>
       <c r="L47" s="6"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
@@ -2105,7 +2102,7 @@
       <c r="K48" s="4"/>
       <c r="L48" s="6"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
@@ -2119,7 +2116,7 @@
       <c r="K49" s="4"/>
       <c r="L49" s="6"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
@@ -2133,7 +2130,7 @@
       <c r="K50" s="4"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
@@ -2147,7 +2144,7 @@
       <c r="K51" s="4"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="5"/>
@@ -2161,7 +2158,7 @@
       <c r="K52" s="4"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
@@ -2175,7 +2172,7 @@
       <c r="K53" s="4"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
@@ -2189,7 +2186,7 @@
       <c r="K54" s="4"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
@@ -2203,7 +2200,7 @@
       <c r="K55" s="4"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
@@ -2217,7 +2214,7 @@
       <c r="K56" s="4"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
@@ -2231,7 +2228,7 @@
       <c r="K57" s="4"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="5"/>
@@ -2245,7 +2242,7 @@
       <c r="K58" s="4"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
@@ -2259,7 +2256,7 @@
       <c r="K59" s="4"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="5"/>
@@ -2273,7 +2270,7 @@
       <c r="K60" s="4"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="5"/>
@@ -2287,7 +2284,7 @@
       <c r="K61" s="4"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="5"/>
@@ -2301,7 +2298,7 @@
       <c r="K62" s="4"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="5"/>
@@ -2315,7 +2312,7 @@
       <c r="K63" s="4"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="5"/>
@@ -2329,7 +2326,7 @@
       <c r="K64" s="4"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="5"/>
@@ -2343,7 +2340,7 @@
       <c r="K65" s="4"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="5"/>
@@ -2357,7 +2354,7 @@
       <c r="K66" s="4"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="5"/>
@@ -2371,7 +2368,7 @@
       <c r="K67" s="4"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="5"/>
@@ -2384,7 +2381,7 @@
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="5"/>
@@ -2397,7 +2394,7 @@
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="5"/>
@@ -2410,7 +2407,7 @@
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="5"/>
@@ -2423,7 +2420,7 @@
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="5"/>
@@ -2436,7 +2433,7 @@
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="5"/>
@@ -2449,7 +2446,7 @@
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="5"/>
@@ -2462,7 +2459,7 @@
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="5"/>
@@ -2475,7 +2472,7 @@
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="5"/>
@@ -2488,7 +2485,7 @@
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="5"/>
@@ -2501,7 +2498,7 @@
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="5"/>
@@ -2514,7 +2511,7 @@
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="5"/>
@@ -2527,7 +2524,7 @@
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="5"/>
@@ -2541,7 +2538,7 @@
       <c r="K80" s="4"/>
     </row>
   </sheetData>
-  <sortState ref="A2:N45">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N45">
     <sortCondition ref="I2:I45"/>
     <sortCondition ref="H2:H45"/>
     <sortCondition ref="G2:G45"/>
